--- a/data/raw/00992A_portfolio_20260604.xlsx
+++ b/data/raw/00992A_portfolio_20260604.xlsx
@@ -384,7 +384,7 @@
         <v>基金淨資產價值(元)</v>
       </c>
       <c r="B1" t="str">
-        <v>TWD 49,619,174,696</v>
+        <v>TWD 48,532,891,227</v>
       </c>
     </row>
     <row r="2">
@@ -392,7 +392,7 @@
         <v>每受益權單位淨資產價值(元)-台幣交易</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD 18.61</v>
+        <v>TWD 18.27</v>
       </c>
     </row>
     <row r="3">
@@ -400,7 +400,7 @@
         <v>已發行受益權單位總數-台幣交易</v>
       </c>
       <c r="B3" t="str">
-        <v>2,665,955,000</v>
+        <v>2,655,955,000</v>
       </c>
     </row>
   </sheetData>
@@ -412,7 +412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>台積電</v>
       </c>
       <c r="C2" t="str">
-        <v>8.34%</v>
+        <v>8.38%</v>
       </c>
       <c r="D2" t="str">
         <v>1,706,000</v>
@@ -444,30 +444,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>3037</v>
+        <v>2383</v>
       </c>
       <c r="B3" t="str">
-        <v>欣興</v>
+        <v>台光電</v>
       </c>
       <c r="C3" t="str">
-        <v>5.64%</v>
+        <v>5.6%</v>
       </c>
       <c r="D3" t="str">
-        <v>2,797,000</v>
+        <v>563,000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2383</v>
+        <v>3037</v>
       </c>
       <c r="B4" t="str">
-        <v>台光電</v>
+        <v>欣興</v>
       </c>
       <c r="C4" t="str">
-        <v>5.48%</v>
+        <v>5.6%</v>
       </c>
       <c r="D4" t="str">
-        <v>563,000</v>
+        <v>2,797,000</v>
       </c>
     </row>
     <row r="5">
@@ -478,7 +478,7 @@
         <v>智邦</v>
       </c>
       <c r="C5" t="str">
-        <v>5.09%</v>
+        <v>5.05%</v>
       </c>
       <c r="D5" t="str">
         <v>977,000</v>
@@ -492,7 +492,7 @@
         <v>緯穎</v>
       </c>
       <c r="C6" t="str">
-        <v>4.36%</v>
+        <v>4.43%</v>
       </c>
       <c r="D6" t="str">
         <v>386,000</v>
@@ -506,7 +506,7 @@
         <v>旺矽</v>
       </c>
       <c r="C7" t="str">
-        <v>3.88%</v>
+        <v>4.08%</v>
       </c>
       <c r="D7" t="str">
         <v>326,000</v>
@@ -514,44 +514,44 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2454</v>
+        <v>8996</v>
       </c>
       <c r="B8" t="str">
-        <v>聯發科</v>
+        <v>高力</v>
       </c>
       <c r="C8" t="str">
-        <v>3.72%</v>
+        <v>3.76%</v>
       </c>
       <c r="D8" t="str">
-        <v>406,000</v>
+        <v>1,630,000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3017</v>
+        <v>2454</v>
       </c>
       <c r="B9" t="str">
-        <v>奇鋐</v>
+        <v>聯發科</v>
       </c>
       <c r="C9" t="str">
-        <v>3.65%</v>
+        <v>3.71%</v>
       </c>
       <c r="D9" t="str">
-        <v>634,000</v>
+        <v>406,000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>8996</v>
+        <v>3017</v>
       </c>
       <c r="B10" t="str">
-        <v>高力</v>
+        <v>奇鋐</v>
       </c>
       <c r="C10" t="str">
-        <v>3.6%</v>
+        <v>3.54%</v>
       </c>
       <c r="D10" t="str">
-        <v>1,630,000</v>
+        <v>634,000</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
         <v>川湖</v>
       </c>
       <c r="C11" t="str">
-        <v>3.36%</v>
+        <v>3.44%</v>
       </c>
       <c r="D11" t="str">
         <v>312,000</v>
@@ -570,30 +570,30 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3665</v>
+        <v>6584</v>
       </c>
       <c r="B12" t="str">
-        <v>貿聯-KY</v>
+        <v>南俊國際</v>
       </c>
       <c r="C12" t="str">
-        <v>3.03%</v>
+        <v>3.04%</v>
       </c>
       <c r="D12" t="str">
-        <v>652,000</v>
+        <v>2,204,000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>6584</v>
+        <v>3665</v>
       </c>
       <c r="B13" t="str">
-        <v>南俊國際</v>
+        <v>貿聯-KY</v>
       </c>
       <c r="C13" t="str">
-        <v>2.93%</v>
+        <v>2.9%</v>
       </c>
       <c r="D13" t="str">
-        <v>2,204,000</v>
+        <v>652,000</v>
       </c>
     </row>
     <row r="14">
@@ -604,7 +604,7 @@
         <v>創意</v>
       </c>
       <c r="C14" t="str">
-        <v>2.89%</v>
+        <v>2.82%</v>
       </c>
       <c r="D14" t="str">
         <v>311,000</v>
@@ -612,30 +612,30 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3661</v>
+        <v>2368</v>
       </c>
       <c r="B15" t="str">
-        <v>世芯-KY</v>
+        <v>金像電</v>
       </c>
       <c r="C15" t="str">
-        <v>2.59%</v>
+        <v>2.63%</v>
       </c>
       <c r="D15" t="str">
-        <v>280,000</v>
+        <v>945,000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2327</v>
+        <v>6515</v>
       </c>
       <c r="B16" t="str">
-        <v>國巨*</v>
+        <v>穎崴</v>
       </c>
       <c r="C16" t="str">
-        <v>2.59%</v>
+        <v>2.58%</v>
       </c>
       <c r="D16" t="str">
-        <v>1,566,000</v>
+        <v>145,000</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         <v>群聯</v>
       </c>
       <c r="C17" t="str">
-        <v>2.57%</v>
+        <v>2.53%</v>
       </c>
       <c r="D17" t="str">
         <v>475,000</v>
@@ -654,44 +654,44 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>6515</v>
+        <v>3661</v>
       </c>
       <c r="B18" t="str">
-        <v>穎崴</v>
+        <v>世芯-KY</v>
       </c>
       <c r="C18" t="str">
-        <v>2.4%</v>
+        <v>2.5%</v>
       </c>
       <c r="D18" t="str">
-        <v>145,000</v>
+        <v>280,000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2455</v>
+        <v>2327</v>
       </c>
       <c r="B19" t="str">
-        <v>全新</v>
+        <v>國巨*</v>
       </c>
       <c r="C19" t="str">
-        <v>2.3%</v>
+        <v>2.4%</v>
       </c>
       <c r="D19" t="str">
-        <v>2,753,000</v>
+        <v>1,566,000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3081</v>
+        <v>2455</v>
       </c>
       <c r="B20" t="str">
-        <v>聯亞</v>
+        <v>全新</v>
       </c>
       <c r="C20" t="str">
-        <v>2.09%</v>
+        <v>2.28%</v>
       </c>
       <c r="D20" t="str">
-        <v>366,000</v>
+        <v>2,753,000</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>日月光投控</v>
       </c>
       <c r="C21" t="str">
-        <v>2.03%</v>
+        <v>1.99%</v>
       </c>
       <c r="D21" t="str">
         <v>1,629,000</v>
@@ -716,7 +716,7 @@
         <v>穩懋</v>
       </c>
       <c r="C22" t="str">
-        <v>2.02%</v>
+        <v>1.96%</v>
       </c>
       <c r="D22" t="str">
         <v>1,949,000</v>
@@ -724,343 +724,371 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2368</v>
+        <v>3081</v>
       </c>
       <c r="B23" t="str">
-        <v>金像電</v>
+        <v>聯亞</v>
       </c>
       <c r="C23" t="str">
-        <v>1.8%</v>
+        <v>1.95%</v>
       </c>
       <c r="D23" t="str">
-        <v>645,000</v>
+        <v>366,000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>6510</v>
+        <v>2308</v>
       </c>
       <c r="B24" t="str">
-        <v>精測</v>
+        <v>台達電</v>
       </c>
       <c r="C24" t="str">
-        <v>1.75%</v>
+        <v>1.72%</v>
       </c>
       <c r="D24" t="str">
-        <v>262,000</v>
+        <v>344,000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2308</v>
+        <v>6274</v>
       </c>
       <c r="B25" t="str">
-        <v>台達電</v>
+        <v>台燿</v>
       </c>
       <c r="C25" t="str">
-        <v>1.7%</v>
+        <v>1.64%</v>
       </c>
       <c r="D25" t="str">
-        <v>344,000</v>
+        <v>471,000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>6274</v>
+        <v>7769</v>
       </c>
       <c r="B26" t="str">
-        <v>台燿</v>
+        <v>鴻勁</v>
       </c>
       <c r="C26" t="str">
-        <v>1.61%</v>
+        <v>1.48%</v>
       </c>
       <c r="D26" t="str">
-        <v>471,000</v>
+        <v>97,000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>7769</v>
+        <v>8046</v>
       </c>
       <c r="B27" t="str">
-        <v>鴻勁</v>
+        <v>南電</v>
       </c>
       <c r="C27" t="str">
-        <v>1.47%</v>
+        <v>1.3%</v>
       </c>
       <c r="D27" t="str">
-        <v>97,000</v>
+        <v>718,000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>8046</v>
+        <v>7751</v>
       </c>
       <c r="B28" t="str">
-        <v>南電</v>
+        <v>竑騰</v>
       </c>
       <c r="C28" t="str">
-        <v>1.31%</v>
+        <v>1.22%</v>
       </c>
       <c r="D28" t="str">
-        <v>718,000</v>
+        <v>375,000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>7751</v>
+        <v>5274</v>
       </c>
       <c r="B29" t="str">
-        <v>竑騰</v>
+        <v>信驊</v>
       </c>
       <c r="C29" t="str">
-        <v>1.19%</v>
+        <v>1.09%</v>
       </c>
       <c r="D29" t="str">
-        <v>375,000</v>
+        <v>29,000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>5274</v>
+        <v>2360</v>
       </c>
       <c r="B30" t="str">
-        <v>信驊</v>
+        <v>致茂</v>
       </c>
       <c r="C30" t="str">
-        <v>1.05%</v>
+        <v>1.08%</v>
       </c>
       <c r="D30" t="str">
-        <v>29,000</v>
+        <v>200,000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2360</v>
+        <v>3583</v>
       </c>
       <c r="B31" t="str">
-        <v>致茂</v>
+        <v>辛耘</v>
       </c>
       <c r="C31" t="str">
-        <v>1.03%</v>
+        <v>1.02%</v>
       </c>
       <c r="D31" t="str">
-        <v>200,000</v>
+        <v>566,000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>3583</v>
+        <v>6187</v>
       </c>
       <c r="B32" t="str">
-        <v>辛耘</v>
+        <v>萬潤</v>
       </c>
       <c r="C32" t="str">
-        <v>0.96%</v>
+        <v>1%</v>
       </c>
       <c r="D32" t="str">
-        <v>566,000</v>
+        <v>435,000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>4991</v>
+        <v>6510</v>
       </c>
       <c r="B33" t="str">
-        <v>環宇-KY</v>
+        <v>精測</v>
       </c>
       <c r="C33" t="str">
-        <v>0.81%</v>
+        <v>0.99%</v>
       </c>
       <c r="D33" t="str">
-        <v>553,000</v>
+        <v>137,000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>3653</v>
+        <v>3008</v>
       </c>
       <c r="B34" t="str">
-        <v>健策</v>
+        <v>大立光</v>
       </c>
       <c r="C34" t="str">
-        <v>0.8%</v>
+        <v>0.99%</v>
       </c>
       <c r="D34" t="str">
-        <v>102,000</v>
+        <v>125,000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>3189</v>
+        <v>3653</v>
       </c>
       <c r="B35" t="str">
-        <v>景碩</v>
+        <v>健策</v>
       </c>
       <c r="C35" t="str">
-        <v>0.7%</v>
+        <v>0.78%</v>
       </c>
       <c r="D35" t="str">
-        <v>470,013</v>
+        <v>102,000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6531</v>
+        <v>4991</v>
       </c>
       <c r="B36" t="str">
-        <v>愛普*</v>
+        <v>環宇-KY</v>
       </c>
       <c r="C36" t="str">
-        <v>0.59%</v>
+        <v>0.78%</v>
       </c>
       <c r="D36" t="str">
-        <v>265,000</v>
+        <v>553,000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>5289</v>
+        <v>3189</v>
       </c>
       <c r="B37" t="str">
-        <v>宜鼎</v>
+        <v>景碩</v>
       </c>
       <c r="C37" t="str">
-        <v>0.58%</v>
+        <v>0.67%</v>
       </c>
       <c r="D37" t="str">
-        <v>153,000</v>
+        <v>470,013</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>8021</v>
+        <v>5289</v>
       </c>
       <c r="B38" t="str">
-        <v>尖點</v>
+        <v>宜鼎</v>
       </c>
       <c r="C38" t="str">
-        <v>0.47%</v>
+        <v>0.6%</v>
       </c>
       <c r="D38" t="str">
-        <v>501,000</v>
+        <v>153,000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2337</v>
+        <v>6531</v>
       </c>
       <c r="B39" t="str">
-        <v>旺宏</v>
+        <v>愛普*</v>
       </c>
       <c r="C39" t="str">
-        <v>0.47%</v>
+        <v>0.58%</v>
       </c>
       <c r="D39" t="str">
-        <v>1,434,000</v>
+        <v>265,000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>6805</v>
+        <v>2337</v>
       </c>
       <c r="B40" t="str">
-        <v>富世達</v>
+        <v>旺宏</v>
       </c>
       <c r="C40" t="str">
         <v>0.46%</v>
       </c>
       <c r="D40" t="str">
-        <v>109,000</v>
+        <v>1,434,000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6139</v>
+        <v>8021</v>
       </c>
       <c r="B41" t="str">
-        <v>亞翔</v>
+        <v>尖點</v>
       </c>
       <c r="C41" t="str">
-        <v>0.4%</v>
+        <v>0.46%</v>
       </c>
       <c r="D41" t="str">
-        <v>250,000</v>
+        <v>501,000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>7734</v>
+        <v>6805</v>
       </c>
       <c r="B42" t="str">
-        <v>印能科技</v>
+        <v>富世達</v>
       </c>
       <c r="C42" t="str">
-        <v>0.37%</v>
+        <v>0.45%</v>
       </c>
       <c r="D42" t="str">
-        <v>56,000</v>
+        <v>109,000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>3260</v>
+        <v>6139</v>
       </c>
       <c r="B43" t="str">
-        <v>威剛</v>
+        <v>亞翔</v>
       </c>
       <c r="C43" t="str">
-        <v>0.36%</v>
+        <v>0.42%</v>
       </c>
       <c r="D43" t="str">
-        <v>382,000</v>
+        <v>250,000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>6442</v>
+        <v>3260</v>
       </c>
       <c r="B44" t="str">
-        <v>光聖</v>
+        <v>威剛</v>
       </c>
       <c r="C44" t="str">
-        <v>0.31%</v>
+        <v>0.36%</v>
       </c>
       <c r="D44" t="str">
-        <v>74,000</v>
+        <v>382,000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>3533</v>
+        <v>7734</v>
       </c>
       <c r="B45" t="str">
-        <v>嘉澤</v>
+        <v>印能科技</v>
       </c>
       <c r="C45" t="str">
-        <v>0.02%</v>
+        <v>0.36%</v>
       </c>
       <c r="D45" t="str">
-        <v>4,000</v>
+        <v>56,000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
+        <v>6442</v>
+      </c>
+      <c r="B46" t="str">
+        <v>光聖</v>
+      </c>
+      <c r="C46" t="str">
+        <v>0.33%</v>
+      </c>
+      <c r="D46" t="str">
+        <v>74,000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>3533</v>
+      </c>
+      <c r="B47" t="str">
+        <v>嘉澤</v>
+      </c>
+      <c r="C47" t="str">
+        <v>0.02%</v>
+      </c>
+      <c r="D47" t="str">
+        <v>4,000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
         <v>3491</v>
       </c>
-      <c r="B46" t="str">
+      <c r="B48" t="str">
         <v>昇達科</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C48" t="str">
         <v>0%</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D48" t="str">
         <v>1,000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1074,7 +1102,7 @@
         <v>應收付證券款</v>
       </c>
       <c r="B1" t="str">
-        <v>TWD 2,451,593,953.00</v>
+        <v>TWD 329,934,502.00</v>
       </c>
     </row>
     <row r="2">
@@ -1082,7 +1110,7 @@
         <v>應付贖回款</v>
       </c>
       <c r="B2" t="str">
-        <v>TWD -2,242,706,535.00</v>
+        <v>TWD -1,942,165,759.00</v>
       </c>
     </row>
     <row r="3">
@@ -1090,7 +1118,7 @@
         <v>現金</v>
       </c>
       <c r="B3" t="str">
-        <v>TWD 2,441,779,994.00</v>
+        <v>TWD 3,139,497,146.00</v>
       </c>
     </row>
   </sheetData>
